--- a/Result/profitability/6958.xlsx
+++ b/Result/profitability/6958.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM17"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,39 +2096,39 @@
         <v>2768</v>
       </c>
       <c r="D14" t="n">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="E14" t="n">
         <v>868</v>
       </c>
       <c r="F14" t="n">
-        <v>31.34</v>
+        <v>31.35</v>
       </c>
       <c r="G14" t="n">
-        <v>-408</v>
+        <v>-409</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-14.75%</t>
+          <t>-14.77%</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>-389</v>
+        <v>-385</v>
       </c>
       <c r="K14" t="n">
-        <v>-225</v>
+        <v>-221</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0.09124999999999998</v>
+        <v>0.09249999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>33.9125</v>
+        <v>33.91375</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2155,28 +2155,28 @@
         <v>114.2</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>0.9642857142857142</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.000000000000004</v>
+        <v>-0.990000000000002</v>
       </c>
       <c r="Z14" t="n">
-        <v>-0.03092145949288816</v>
+        <v>-0.03061224489795922</v>
       </c>
       <c r="AA14" t="n">
-        <v>-1.06</v>
+        <v>-1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>-2.12</v>
+        <v>-2.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>-3.190000000000001</v>
+        <v>-3.18</v>
       </c>
       <c r="AD14" t="n">
-        <v>-0.09238343469446864</v>
+        <v>-0.09209383145091221</v>
       </c>
       <c r="AE14" t="n">
         <v>0</v>
@@ -2226,7 +2226,7 @@
         <v>1848</v>
       </c>
       <c r="E15" t="n">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F15" t="n">
         <v>28.72</v>
@@ -2240,22 +2240,22 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>-566</v>
+        <v>-570</v>
       </c>
       <c r="K15" t="n">
-        <v>-357</v>
+        <v>-361</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="M15" t="n">
         <v>-0.06500000000000002</v>
       </c>
       <c r="N15" t="n">
-        <v>33.2375</v>
+        <v>33.23875</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2282,22 +2282,22 @@
         <v>114.3</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.32</v>
+        <v>-0.34</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="Y15" t="n">
-        <v>-2.620000000000001</v>
+        <v>-2.630000000000003</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.0835992342054882</v>
+        <v>-0.08389154704944191</v>
       </c>
       <c r="AA15" t="n">
-        <v>-1.29</v>
+        <v>-1.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>-3.146341463414634</v>
+        <v>-3.170731707317073</v>
       </c>
       <c r="AC15" t="n">
         <v>-5.289999999999999</v>
@@ -2382,7 +2382,7 @@
         <v>-0.155</v>
       </c>
       <c r="N16" t="n">
-        <v>32.5325</v>
+        <v>32.53375</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2409,10 +2409,10 @@
         <v>114.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2386363636363636</v>
+        <v>-0.247191011235955</v>
       </c>
       <c r="Y16" t="n">
         <v>1.240000000000002</v>
@@ -2509,7 +2509,7 @@
         <v>-0.16875</v>
       </c>
       <c r="N17" t="n">
-        <v>31.73875</v>
+        <v>31.74</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
@@ -2587,6 +2587,133 @@
       </c>
       <c r="AM17" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6958</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2528</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E18" t="n">
+        <v>708</v>
+      </c>
+      <c r="F18" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="G18" t="n">
+        <v>161</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6.36%</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="n">
+        <v>175</v>
+      </c>
+      <c r="K18" t="n">
+        <v>103</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-0.19875</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30.9225</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-0.360000000000003</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-0.01269841269841276</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-1.472727272727273</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-3.360000000000003</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0.107177033492823</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
